--- a/my-vocab-sheet.xlsx
+++ b/my-vocab-sheet.xlsx
@@ -3961,7 +3961,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>&lt;svg xmlns="http://www.w3.org/2000/svg" viewBox="0 0 360 260" width="100%" style="max-width:340px" font-family="inherit"&gt;&lt;text x="10" y="16" font-size="9" letter-spacing="1" fill="currentColor" fill-opacity=".55"&gt;MEANING&lt;/text&gt;&lt;line x1="40" y1="110" x2="320" y2="110" stroke="currentColor" stroke-opacity=".5" stroke-width="1.5" /&gt;&lt;rect x="150" y="38" width="100" height="42" rx="4" fill="#f08c00" /&gt;&lt;rect x="250" y="54" width="80" height="10" rx="3" fill="currentColor" fill-opacity=".6" /&gt;&lt;g stroke="currentColor" stroke-opacity=".4" stroke-width="1.5"&gt;&lt;line x1="160" y1="30" x2="175" y2="24" /&gt;&lt;line x1="200" y1="28" x2="200" y2="20" /&gt;&lt;line x1="240" y1="30" x2="225" y2="24" /&gt;&lt;/g&gt;&lt;polygon points="195,88 205,88 200,96" fill="currentColor" fill-opacity=".6" /&gt;&lt;circle cx="200" cy="104" r="6" fill="none" stroke="currentColor" stroke-width="1.5" /&gt;&lt;text x="145" y="64" font-size="11" text-anchor="end" fill="#f08c00"&gt;huge force&lt;/text&gt;&lt;text x="200" y="125" font-size="11" text-anchor="middle" fill="currentColor"&gt;tiny task&lt;/text&gt;&lt;line x1="0" y1="130" x2="360" y2="130" stroke="currentColor" stroke-opacity=".2" /&gt;&lt;text x="10" y="146" font-size="9" letter-spacing="1" fill="currentColor" fill-opacity=".55"&gt;EXAMPLE&lt;/text&gt;&lt;rect x="20" y="156" width="145" height="82" rx="4" fill="none" stroke="currentColor" stroke-opacity=".6" /&gt;&lt;polyline points="32,204 60,190 88,196 116,176 150,168" fill="none" stroke="currentColor" stroke-width="1.5" /&gt;&lt;rect x="28" y="214" width="129" height="16" rx="3" fill="#f08c00" fill-opacity=".15" stroke="#f08c00" /&gt;&lt;polygon points="34,217 34,227 42,222" fill="#f08c00" /&gt;&lt;polygon points="56,222 63,217 63,227" fill="#f08c00" /&gt;&lt;line x1="54" y1="217" x2="54" y2="227" stroke="#f08c00" stroke-width="1.5" /&gt;&lt;polygon points="74,217 74,227 81,222" fill="#f08c00" /&gt;&lt;line x1="83" y1="217" x2="83" y2="227" stroke="#f08c00" stroke-width="1.5" /&gt;&lt;line x1="92" y1="222" x2="150" y2="222" stroke="#f08c00" stroke-opacity=".5" stroke-width="2" /&gt;&lt;circle cx="110" cy="222" r="3" fill="#f08c00" /&gt;&lt;text x="92" y="253" font-size="11" text-anchor="middle" fill="currentColor"&gt;step player =&lt;tspan fill="#f08c00" font-weight="bold"&gt;overkill&lt;/tspan&gt;&lt;/text&gt;&lt;rect x="195" y="156" width="145" height="82" rx="4" fill="none" stroke="currentColor" stroke-opacity=".6" /&gt;&lt;line x1="205" y1="228" x2="330" y2="228" stroke="currentColor" stroke-opacity=".5" /&gt;&lt;rect x="215" y="208" width="24" height="20" fill="#37b24d" /&gt;&lt;rect x="255" y="188" width="24" height="40" fill="#37b24d" /&gt;&lt;rect x="295" y="173" width="24" height="55" fill="#37b24d" /&gt;&lt;text x="227" y="204" font-size="10" text-anchor="middle" fill="currentColor"&gt;12&lt;/text&gt;&lt;text x="267" y="184" font-size="10" text-anchor="middle" fill="currentColor"&gt;40&lt;/text&gt;&lt;text x="307" y="169" font-size="10" text-anchor="middle" fill="currentColor"&gt;85&lt;/text&gt;&lt;text x="267" y="253" font-size="10" text-anchor="middle" fill="#37b24d"&gt;still + numbers: faster&lt;/text&gt;&lt;/svg&gt;</t>
+          <t>&lt;svg xmlns="http://www.w3.org/2000/svg" viewBox="0 0 360 280" width="100%" style="max-width:340px" font-family="inherit"&gt;&lt;text x="10" y="16" font-size="9" letter-spacing="1" fill="currentColor" fill-opacity=".55"&gt;MEANING&lt;/text&gt;&lt;line x1="40" y1="121" x2="320" y2="121" stroke="currentColor" stroke-opacity=".5" stroke-width="1.5" /&gt;&lt;rect x="195" y="22" width="10" height="30" rx="2" fill="currentColor" fill-opacity=".6" /&gt;&lt;rect x="150" y="50" width="100" height="42" rx="4" fill="#f08c00" /&gt;&lt;line x1="200" y1="96" x2="200" y2="104" stroke="currentColor" stroke-width="1.5" /&gt;&lt;polygon points="196,103 204,103 200,108" fill="currentColor" /&gt;&lt;line x1="182" y1="98" x2="176" y2="104" stroke="currentColor" stroke-opacity=".5" /&gt;&lt;line x1="218" y1="98" x2="224" y2="104" stroke="currentColor" stroke-opacity=".5" /&gt;&lt;ellipse cx="200" cy="116" rx="6" ry="5" fill="currentColor" /&gt;&lt;text x="60" y="76" font-size="12" fill="currentColor"&gt;huge force&lt;/text&gt;&lt;text x="214" y="118" font-size="11" fill="currentColor" fill-opacity=".8"&gt;tiny task&lt;/text&gt;&lt;text x="264" y="76" font-size="12" fill="#f08c00" font-weight="bold"&gt;= overkill&lt;/text&gt;&lt;line x1="0" y1="140" x2="360" y2="140" stroke="currentColor" stroke-opacity=".2" /&gt;&lt;text x="10" y="156" font-size="9" letter-spacing="1" fill="currentColor" fill-opacity=".55"&gt;EXAMPLE&lt;/text&gt;&lt;rect x="20" y="164" width="150" height="86" rx="4" fill="none" stroke="#f08c00" stroke-width="1.5" /&gt;&lt;rect x="40" y="200" width="22" height="25" fill="currentColor" fill-opacity=".25" /&gt;&lt;rect x="72" y="185" width="22" height="40" fill="currentColor" fill-opacity=".25" /&gt;&lt;rect x="104" y="193" width="22" height="32" fill="currentColor" fill-opacity=".25" /&gt;&lt;rect x="28" y="231" width="134" height="13" rx="3" fill="currentColor" fill-opacity=".12" /&gt;&lt;polygon points="33,234 33,241 39,237.5" fill="currentColor" /&gt;&lt;polygon points="43,234 43,241 49,237.5" fill="currentColor" /&gt;&lt;line x1="56" y1="237.5" x2="154" y2="237.5" stroke="currentColor" stroke-opacity=".5" stroke-width="2" /&gt;&lt;circle cx="84" cy="237.5" r="3.5" fill="#f08c00" /&gt;&lt;rect x="190" y="164" width="150" height="86" rx="4" fill="none" stroke="currentColor" stroke-opacity=".6" stroke-width="1.5" /&gt;&lt;rect x="212" y="213" width="24" height="27" fill="#339af0" /&gt;&lt;rect x="252" y="190" width="24" height="50" fill="#339af0" /&gt;&lt;rect x="292" y="203" width="24" height="37" fill="#339af0" /&gt;&lt;text x="224" y="209" font-size="10" text-anchor="middle" fill="currentColor"&gt;12&lt;/text&gt;&lt;text x="264" y="186" font-size="10" text-anchor="middle" fill="currentColor"&gt;40&lt;/text&gt;&lt;text x="304" y="199" font-size="10" text-anchor="middle" fill="currentColor"&gt;25&lt;/text&gt;&lt;circle cx="324" cy="178" r="8" fill="#37b24d" /&gt;&lt;polyline points="320,178 323,181 328,175" fill="none" stroke="#fff" stroke-width="2" /&gt;&lt;text x="95" y="267" font-size="11" text-anchor="middle" fill="currentColor"&gt;step player: &lt;tspan fill="#f08c00" font-weight="bold"&gt;overkill&lt;/tspan&gt;&lt;/text&gt;&lt;text x="265" y="267" font-size="11" text-anchor="middle" fill="currentColor"&gt;one still picture&lt;/text&gt;&lt;/svg&gt;</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>&lt;svg xmlns="http://www.w3.org/2000/svg" viewBox="0 0 360 280" width="100%" style="max-width:340px" font-family="inherit"&gt;&lt;text x="8" y="16" font-size="9" letter-spacing="1" fill="currentColor" fill-opacity=".55"&gt;MEANING&lt;/text&gt;&lt;rect x="20" y="50" width="140" height="24" fill="none" stroke="currentColor" stroke-width="2" /&gt;&lt;path d="M58 50 L64 62 L58 74" fill="none" stroke="currentColor" stroke-opacity=".4" /&gt;&lt;rect x="50" y="44" width="24" height="36" fill="#f08c00" rx="2" /&gt;&lt;line x1="50" y1="56" x2="74" y2="56" stroke="#fff" stroke-opacity=".6" /&gt;&lt;line x1="50" y1="68" x2="74" y2="68" stroke="#fff" stroke-opacity=".6" /&gt;&lt;circle cx="62" cy="88" r="2" fill="#339af0" fill-opacity=".5" /&gt;&lt;text x="90" y="104" font-size="12" text-anchor="middle" fill="#f08c00"&gt;stop-gap (now)&lt;/text&gt;&lt;line x1="170" y1="62" x2="196" y2="62" stroke="currentColor" stroke-opacity=".6" stroke-width="1.5" /&gt;&lt;polygon points="204,62 195,57 195,67" fill="currentColor" fill-opacity=".6" /&gt;&lt;rect x="212" y="50" width="128" height="24" fill="none" stroke="currentColor" stroke-width="2" stroke-opacity=".5" /&gt;&lt;rect x="258" y="47" width="30" height="30" fill="#37b24d" fill-opacity=".2" stroke="#37b24d" stroke-width="2" stroke-dasharray="4 3" /&gt;&lt;text x="276" y="104" font-size="12" text-anchor="middle" fill="currentColor" fill-opacity=".8"&gt;proper fix (later)&lt;/text&gt;&lt;line x1="0" y1="140" x2="360" y2="140" stroke="currentColor" stroke-opacity=".2" /&gt;&lt;text x="8" y="156" font-size="9" letter-spacing="1" fill="currentColor" fill-opacity=".55"&gt;EXAMPLE&lt;/text&gt;&lt;rect x="16" y="164" width="328" height="106" rx="4" fill="none" stroke="currentColor" stroke-opacity=".4" /&gt;&lt;text x="26" y="184" font-size="11" fill="currentColor" fill-opacity=".6"&gt;--&lt;tspan fill="#f08c00" fill-opacity="1"&gt;Stop-gap&lt;/tspan&gt;until the monitoring&lt;/text&gt;&lt;text x="26" y="199" font-size="11" fill="currentColor" fill-opacity=".6"&gt;-- permission set is decided.&lt;/text&gt;&lt;rect x="24" y="210" width="172" height="24" rx="3" fill="#f08c00" fill-opacity=".15" stroke="#f08c00" /&gt;&lt;text x="32" y="226" font-size="11" fill="currentColor"&gt;GRANT SELECT TO monitor;&lt;/text&gt;&lt;rect x="222" y="210" width="114" height="24" rx="3" fill="none" stroke="#339af0" stroke-dasharray="4 3" /&gt;&lt;text x="279" y="226" font-size="11" text-anchor="middle" fill="#339af0"&gt;permission set?&lt;/text&gt;&lt;line x1="220" y1="222" x2="206" y2="222" stroke="#339af0" stroke-width="1.5" /&gt;&lt;polygon points="198,222 206,217 206,227" fill="#339af0" /&gt;&lt;text x="279" y="254" font-size="10" text-anchor="middle" fill="currentColor" fill-opacity=".6"&gt;replaces it later&lt;/text&gt;&lt;/svg&gt;</t>
+          <t>&lt;svg xmlns="http://www.w3.org/2000/svg" viewBox="0 0 360 260" width="100%" style="max-width:340px" font-family="inherit"&gt;&lt;text x="10" y="16" font-size="9" letter-spacing="1" fill="currentColor" fill-opacity=".55"&gt;MEANING&lt;/text&gt;&lt;rect x="20" y="64" width="80" height="22" fill="currentColor" fill-opacity=".15" stroke="currentColor" /&gt;&lt;rect x="120" y="64" width="80" height="22" fill="currentColor" fill-opacity=".15" stroke="currentColor" /&gt;&lt;rect x="92" y="57" width="36" height="36" rx="3" fill="#f08c00" /&gt;&lt;line x1="96" y1="62" x2="124" y2="88" stroke="#fff" stroke-opacity=".6" stroke-width="2" /&gt;&lt;line x1="124" y1="62" x2="96" y2="88" stroke="#fff" stroke-opacity=".6" stroke-width="2" /&gt;&lt;text x="110" y="47" font-size="13" text-anchor="middle" fill="#f08c00" font-weight="bold"&gt;stop-gap&lt;/text&gt;&lt;text x="110" y="112" font-size="10" text-anchor="middle" fill="currentColor" fill-opacity=".7"&gt;tape for now&lt;/text&gt;&lt;rect x="260" y="64" width="70" height="22" fill="none" stroke="#37b24d" stroke-dasharray="4 3" /&gt;&lt;text x="295" y="112" font-size="10" text-anchor="middle" fill="#37b24d"&gt;proper fix, later&lt;/text&gt;&lt;path d="M258 60 Q200 30 140 52" fill="none" stroke="currentColor" stroke-opacity=".5" stroke-dasharray="3 3" /&gt;&lt;polygon points="134,55 143,47 145,56" fill="currentColor" fill-opacity=".5" /&gt;&lt;line x1="0" y1="130" x2="360" y2="130" stroke="currentColor" stroke-opacity=".2" /&gt;&lt;text x="10" y="146" font-size="9" letter-spacing="1" fill="currentColor" fill-opacity=".55"&gt;EXAMPLE&lt;/text&gt;&lt;rect x="20" y="154" width="320" height="94" rx="4" fill="none" stroke="currentColor" stroke-opacity=".4" /&gt;&lt;text x="30" y="170" font-size="10" fill="currentColor" fill-opacity=".55"&gt;setup.sql&lt;/text&gt;&lt;text x="30" y="188" font-size="11" fill="currentColor" fill-opacity=".75"&gt;-- &lt;tspan fill="#f08c00" font-weight="bold"&gt;Stop-gap&lt;/tspan&gt; until the monitoring&lt;/text&gt;&lt;text x="30" y="202" font-size="11" fill="currentColor" fill-opacity=".75"&gt;-- permission set is decided.&lt;/text&gt;&lt;rect x="26" y="212" width="164" height="22" rx="3" fill="#f08c00" /&gt;&lt;text x="108" y="227" font-size="11" text-anchor="middle" fill="#fff"&gt;GRANT SELECT TO monitor;&lt;/text&gt;&lt;rect x="214" y="212" width="116" height="22" rx="3" fill="none" stroke="#37b24d" stroke-dasharray="4 3" /&gt;&lt;text x="272" y="227" font-size="10" text-anchor="middle" fill="#37b24d"&gt;permission set: ?&lt;/text&gt;&lt;line x1="212" y1="223" x2="199" y2="223" stroke="currentColor" stroke-opacity=".5" /&gt;&lt;polygon points="193,223 200,219 200,227" fill="currentColor" fill-opacity=".5" /&gt;&lt;/svg&gt;</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
